--- a/lucas/import_data/utility/observation/excel/provision.xlsx
+++ b/lucas/import_data/utility/observation/excel/provision.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="138">
   <si>
     <t xml:space="preserve">provider_id__provider_name</t>
   </si>
@@ -61,6 +61,12 @@
     <t xml:space="preserve">document</t>
   </si>
   <si>
+    <t xml:space="preserve">senses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auxiliary</t>
+  </si>
+  <si>
     <t xml:space="preserve">metrohm</t>
   </si>
   <si>
@@ -401,6 +407,33 @@
   </si>
   <si>
     <t xml:space="preserve">LIBS laboratory grade spectrometer in UV-VIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human interpreter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human interpretation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human sensing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human interpretation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human interpretation of usually nominal conditions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eu-eea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compilation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compilation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compilation of several data sources</t>
   </si>
 </sst>
 </file>
@@ -410,7 +443,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -431,6 +464,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -475,7 +513,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -489,6 +527,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -512,37 +554,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -615,8 +657,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:O29"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27.62"/>
@@ -667,28 +709,34 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="0" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J2" s="1" t="n">
         <v>1</v>
@@ -697,25 +745,25 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J3" s="1" t="n">
         <v>1</v>
@@ -724,25 +772,25 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -754,25 +802,25 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>1</v>
@@ -780,25 +828,25 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J6" s="1" t="n">
         <v>1</v>
@@ -806,25 +854,25 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J7" s="1" t="n">
         <v>1</v>
@@ -832,25 +880,25 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J8" s="1" t="n">
         <v>1</v>
@@ -858,25 +906,25 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>1</v>
@@ -887,25 +935,25 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>1</v>
@@ -916,25 +964,25 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>1</v>
@@ -942,25 +990,25 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>1</v>
@@ -968,25 +1016,25 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J13" s="1" t="n">
         <v>1</v>
@@ -994,25 +1042,25 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>1</v>
@@ -1023,25 +1071,25 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>1</v>
@@ -1052,25 +1100,25 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>1</v>
@@ -1078,25 +1126,25 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I17" s="1" t="n">
         <v>1</v>
@@ -1104,25 +1152,25 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="I18" s="1" t="n">
         <v>1</v>
@@ -1130,25 +1178,25 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>1</v>
@@ -1156,25 +1204,25 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="I20" s="1" t="n">
         <v>1</v>
@@ -1182,25 +1230,25 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="n">
@@ -1209,25 +1257,25 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>1</v>
@@ -1235,25 +1283,25 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>1</v>
@@ -1267,25 +1315,25 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J24" s="1" t="n">
         <v>1</v>
@@ -1293,25 +1341,25 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="J25" s="1" t="n">
         <v>1</v>
@@ -1319,25 +1367,25 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J26" s="1" t="n">
         <v>1</v>
@@ -1345,27 +1393,79 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J27" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N28" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="O29" s="0" t="n">
         <v>1</v>
       </c>
     </row>

--- a/lucas/import_data/utility/observation/excel/provision.xlsx
+++ b/lucas/import_data/utility/observation/excel/provision.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
   <si>
     <t xml:space="preserve">provider_id__provider_name</t>
   </si>
@@ -37,6 +37,9 @@
     <t xml:space="preserve">alias</t>
   </si>
   <si>
+    <t xml:space="preserve">tag</t>
+  </si>
+  <si>
     <t xml:space="preserve">display_name</t>
   </si>
   <si>
@@ -73,13 +76,16 @@
     <t xml:space="preserve">wetlab</t>
   </si>
   <si>
-    <t xml:space="preserve">lucas-wetlab-2009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lucas-soillab-2009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUCAS-wetlab-2009</t>
+    <t xml:space="preserve">lucas wetlab 2009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lucas soillab 2009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lucas-lab-2009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS wetlab 2009</t>
   </si>
   <si>
     <t xml:space="preserve">Laboratory analysis package employed by the EU wide LUCAS 2009 soil sampling and analysis campaign</t>
@@ -88,13 +94,16 @@
     <t xml:space="preserve">lucas-laboratory-2015</t>
   </si>
   <si>
-    <t xml:space="preserve">lucas-wetlab-2015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lucas-soillab-2015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUCAS-wetlab-2015</t>
+    <t xml:space="preserve">lucas wetlab 2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lucas soillab 2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lucas-lab-2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS wetlab 2015</t>
   </si>
   <si>
     <t xml:space="preserve">Laboratory analysis package employed by the EU wide LUCAS 2015 soil sampling and analysis campaign</t>
@@ -112,6 +121,9 @@
     <t xml:space="preserve">foss xds rca</t>
   </si>
   <si>
+    <t xml:space="preserve">foss-xds-rca</t>
+  </si>
+  <si>
     <t xml:space="preserve">FOSS XDS RCA</t>
   </si>
   <si>
@@ -127,6 +139,9 @@
     <t xml:space="preserve">human sensing</t>
   </si>
   <si>
+    <t xml:space="preserve">hum-sens</t>
+  </si>
+  <si>
     <t xml:space="preserve">Human interpretation</t>
   </si>
   <si>
@@ -137,6 +152,9 @@
   </si>
   <si>
     <t xml:space="preserve">compilation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compilat</t>
   </si>
   <si>
     <t xml:space="preserve">Compilation</t>
@@ -357,7 +375,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.44"/>
@@ -365,8 +383,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="27.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="32.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="27.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="32.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -415,139 +433,157 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="1" t="n">
+      <c r="J3" s="1"/>
+      <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="1"/>
       <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O5" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O6" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P6" s="1" t="n">
         <v>1</v>
       </c>
     </row>
